--- a/business_forms/031_heuristic_evaluation_checklist--business_forms.xlsx
+++ b/business_forms/031_heuristic_evaluation_checklist--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Search Box</t>
+          <t>Search Box Rating</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>User Experience</t>
+          <t>User Experience Rating</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Navigation Rating</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>search_box_rating</t>
+          <t>search_box_rating_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Search Box</t>
+          <t>Search Box Rating 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>error_message</t>
+          <t>error_message_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Error Message</t>
+          <t>Error Message 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>user_characteristics</t>
+          <t>user_characteristics_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>User Characteristics</t>
+          <t>User Characteristics 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>feedback_form</t>
+          <t>feedback_form_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Feedback Form</t>
+          <t>Feedback Form 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prophets</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Prophets</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>search_results</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Search Results</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>user_experience</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>User Experience</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>search_box</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Search Box</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>user_experience_rating</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>User Experience</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>navigation_rating</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Navigation</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>simple_goal_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Simple Goal 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1148,267 +987,148 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>simple_goal_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Simple Goal 2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>simple_user_goals_choices</t>
+          <t>simple_task_completion_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>simple_goal_3</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Simple Goal 3</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>simple_user_goals_choices</t>
+          <t>simple_task_completion_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>simple_goal_4</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Simple Goal 4</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>simple_user_goals_choices</t>
+          <t>feedback_form_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>simple_goal_5</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Simple Goal 5</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>simple_task_completion_choices</t>
+          <t>feedback_form_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>simple_task_completion_choices</t>
+          <t>prophets_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>simple_task_completion_choices</t>
+          <t>prophets_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>feedback_form_choices</t>
+          <t>feedback_form_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>feedback_form_choices</t>
+          <t>feedback_form_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>prophets_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>prophet_1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Prophet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>prophets_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>prophet_2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Prophet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>prophets_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>prophet_3</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Prophet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>feedback_form_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>feedback_form_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>prophets_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>prophets_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
